--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104490_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104490_W4.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0015</v>
+        <v>4.8529</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3375</v>
+        <v>3.3908</v>
       </c>
       <c r="F2" t="n">
-        <v>1.664</v>
+        <v>1.4621</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3062</v>
+        <v>4.1121</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8024</v>
+        <v>0.7351</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5038</v>
+        <v>3.3769</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0865</v>
+        <v>4.2087</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9772</v>
+        <v>0.8651</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1092</v>
+        <v>3.3436</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2197</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1749</v>
+        <v>-0.13</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3946</v>
+        <v>0.0333</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6621</v>
+        <v>0.2254</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3852</v>
+        <v>-0.3627</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2769</v>
+        <v>0.5881</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3278</v>
+        <v>0.0601</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.4205</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3126</v>
+        <v>4.5242</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9435</v>
+        <v>3.1985</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3691</v>
+        <v>1.3257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1102</v>
+        <v>2.3051</v>
       </c>
       <c r="H3" t="n">
-        <v>0.733</v>
+        <v>1.7954</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3772</v>
+        <v>0.5097</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2318</v>
+        <v>2.0583</v>
       </c>
       <c r="K3" t="n">
-        <v>0.876</v>
+        <v>1.9543</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3558</v>
+        <v>0.104</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1216</v>
+        <v>0.2468</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1431</v>
+        <v>-0.1588</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0214</v>
+        <v>0.4057</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3091</v>
+        <v>1.1801</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8347</v>
+        <v>0.2783</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5256</v>
+        <v>0.9018</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0578</v>
+        <v>-0.3268</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0578</v>
+        <v>-1.4163</v>
       </c>
     </row>
     <row r="4">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6201</v>
+        <v>1.8874</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3622</v>
+        <v>0.4483</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2579</v>
+        <v>1.4391</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7891</v>
+        <v>2.7851</v>
       </c>
       <c r="H4" t="n">
-        <v>2.352</v>
+        <v>2.3549</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4371</v>
+        <v>0.4302</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9057</v>
+        <v>2.8805</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6451</v>
+        <v>1.6375</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2607</v>
+        <v>1.243</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1167</v>
+        <v>-0.0954</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1921</v>
+        <v>0.4681</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0484</v>
+        <v>0.0717</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2404</v>
+        <v>0.3964</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.977</v>
+        <v>0.9305</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4898</v>
+        <v>0.0333</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4668</v>
+        <v>0.8973</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3632</v>
+        <v>2.0324</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6941000000000001</v>
+        <v>-1.1148</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6691</v>
+        <v>3.1472</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6163</v>
+        <v>2.3592</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6163</v>
+        <v>-0.5968</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.9559</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7469</v>
+        <v>-0.3268</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.518</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6691</v>
+        <v>0.1912</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4537</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0738</v>
+        <v>0.0476</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1603</v>
+        <v>-0.1375</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.1851</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0113</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3278</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5336</v>
+        <v>0.8095</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1088</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6424</v>
+        <v>1.6738</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0332</v>
+        <v>1.3689</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1227</v>
+        <v>0.6923</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1559</v>
+        <v>0.6766</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3916</v>
+        <v>0.6065</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5857</v>
+        <v>0.6065</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9772</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3584</v>
+        <v>0.7623</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5371</v>
+        <v>0.0857</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1787</v>
+        <v>0.6766</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.359</v>
+        <v>-0.0929</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3266</v>
+        <v>-0.193</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0324</v>
+        <v>0.1002</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0064</v>
+        <v>-0.0113</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3278</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0365</v>
+        <v>-0.4253</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7513</v>
+        <v>-1.9172</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7877999999999999</v>
+        <v>1.4919</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6124000000000001</v>
+        <v>-1.1495</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4387</v>
+        <v>0.7752</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8263</v>
+        <v>-1.9247</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9182</v>
+        <v>-1.5992</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.1444</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0027</v>
+        <v>-1.7436</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3057</v>
+        <v>0.4497</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5178</v>
+        <v>0.6308</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8236</v>
+        <v>-0.1811</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5848</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5989</v>
+        <v>0.0297</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9859</v>
+        <v>-0.0959</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2534</v>
+        <v>1.018</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.018</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0977</v>
+        <v>-0.8688</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5198</v>
+        <v>-1.0634</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4221</v>
+        <v>0.1946</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5327</v>
+        <v>0.6129</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8587</v>
+        <v>1.4335</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.674</v>
+        <v>-0.8205</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4515</v>
+        <v>0.8952</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6998</v>
+        <v>0.9028</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7517</v>
+        <v>-0.0077</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0812</v>
+        <v>-0.2822</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.159</v>
+        <v>0.5306</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9222</v>
+        <v>-0.8129</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5692</v>
+        <v>0.6761</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1875</v>
+        <v>0.3178</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7567</v>
+        <v>0.3583</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1207</v>
+        <v>-1.0333</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2971</v>
+        <v>-1.4222</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1764</v>
+        <v>0.3889</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1514</v>
+        <v>-2.5222</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7705</v>
+        <v>-0.8479</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9219</v>
+        <v>-1.6743</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5684</v>
+        <v>-1.4635</v>
       </c>
       <c r="K9" t="n">
-        <v>0.159</v>
+        <v>-0.7035</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7274</v>
+        <v>-0.7601</v>
       </c>
       <c r="M9" t="n">
-        <v>0.417</v>
+        <v>-1.0587</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6115</v>
+        <v>-0.1444</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1945</v>
+        <v>-0.9143</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7709</v>
+        <v>0.6271</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3962</v>
+        <v>-0.0678</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3747</v>
+        <v>0.6948</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0285</v>
+        <v>1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0285</v>
+        <v>1.2472</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6257</v>
+        <v>-1.5177</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4182</v>
+        <v>-0.4072</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2075</v>
+        <v>-1.1104</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2463</v>
+        <v>2.6613</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3449</v>
+        <v>-0.7761</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09859999999999999</v>
+        <v>3.4374</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0173</v>
+        <v>2.3014</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0173</v>
+        <v>-0.6173</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.9187</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2636</v>
+        <v>0.3598</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3622</v>
+        <v>-0.1588</v>
       </c>
       <c r="O10" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.5187</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0599</v>
+        <v>-0.2276</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>-0.4324</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1488</v>
+        <v>0.2047</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-3.2684</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3134</v>
+        <v>-1.5623</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9155</v>
+        <v>-0.3011</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.398</v>
+        <v>-1.2612</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6637</v>
+        <v>-0.2405</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.788</v>
+        <v>-0.3419</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4517</v>
+        <v>0.1014</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3267</v>
+        <v>0.0172</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6132</v>
+        <v>0.0172</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9399</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.337</v>
+        <v>-0.2578</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1749</v>
+        <v>-0.3592</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5118</v>
+        <v>0.1014</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0186</v>
+        <v>-0.0046</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9739</v>
+        <v>-0.0907</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0448</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.278</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.278</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4771</v>
+        <v>-2.3979</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6094</v>
+        <v>-3.52</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1323</v>
+        <v>1.1222</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.3636</v>
+        <v>-3.3659</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.2624</v>
+        <v>-3.2708</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1012</v>
+        <v>-0.0951</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9669</v>
+        <v>-2.9807</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.0415</v>
+        <v>-3.0551</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3967</v>
+        <v>-0.3852</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.039</v>
+        <v>0.0476</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6566</v>
+        <v>0.6262</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9256</v>
+        <v>0.9204</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4885</v>
+        <v>-0.4846</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.846700000000002</v>
+        <v>5.199199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.466699999999999</v>
+        <v>-2.4246</v>
       </c>
       <c r="F13" t="n">
-        <v>7.313300000000001</v>
+        <v>7.624</v>
       </c>
       <c r="G13" t="n">
-        <v>8.584000000000001</v>
+        <v>8.5997</v>
       </c>
       <c r="H13" t="n">
-        <v>1.414</v>
+        <v>1.434900000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>7.17</v>
+        <v>7.1648</v>
       </c>
       <c r="J13" t="n">
-        <v>9.507300000000001</v>
+        <v>9.2836</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2716</v>
+        <v>1.1551</v>
       </c>
       <c r="L13" t="n">
-        <v>8.2356</v>
+        <v>8.128299999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9233000000000002</v>
+        <v>-0.6841999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1418999999999998</v>
+        <v>0.2796</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0656</v>
+        <v>-0.9637999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4024</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8783</v>
+        <v>-15.9341</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5255</v>
+        <v>2.8807</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5272</v>
+        <v>-1.1652</v>
       </c>
       <c r="U13" t="n">
-        <v>4.0525</v>
+        <v>4.045699999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.8601</v>
+        <v>-2.8665</v>
       </c>
       <c r="W13" t="n">
-        <v>5.4315</v>
+        <v>5.3907</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.291600000000001</v>
+        <v>-8.257299999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9788</v>
+        <v>3.1071</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0041</v>
+        <v>1.8303</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0254</v>
+        <v>1.2769</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2804</v>
+        <v>-3.2685</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7953</v>
+        <v>0.0955</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4851</v>
+        <v>-3.364</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3357</v>
+        <v>-1.8535</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8906</v>
+        <v>0.4267</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4451</v>
+        <v>-2.2802</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0554</v>
+        <v>-1.415</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0954</v>
+        <v>-0.3312</v>
       </c>
       <c r="O14" t="n">
-        <v>0.04</v>
+        <v>-1.0838</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3374</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6684</v>
+        <v>-0.6741</v>
       </c>
       <c r="U14" t="n">
-        <v>0.669</v>
+        <v>-0.1308</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0927</v>
+        <v>5.1318</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.3579</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5363</v>
+        <v>2.0351</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3087</v>
+        <v>2.1378</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2276</v>
+        <v>-0.1027</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4752</v>
+        <v>0.4694</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1256</v>
+        <v>1.1204</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6504</v>
+        <v>-0.651</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0676</v>
+        <v>3.0292</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2845</v>
+        <v>1.2648</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7831</v>
+        <v>1.7644</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5924</v>
+        <v>-2.5598</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.4335</v>
+        <v>-2.4154</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5148</v>
+        <v>0.021</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2903</v>
+        <v>-0.407</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8051</v>
+        <v>0.428</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4453</v>
+        <v>1.7683</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4256</v>
+        <v>2.1513</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0197</v>
+        <v>-0.383</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.2449</v>
+        <v>2.2655</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1084</v>
+        <v>1.7814</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.3533</v>
+        <v>0.4841</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.7988</v>
+        <v>2.3073</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4565</v>
+        <v>1.8681</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.2552</v>
+        <v>0.4392</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4461</v>
+        <v>-0.0417</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.348</v>
+        <v>-0.0866</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0981</v>
+        <v>0.0449</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4932</v>
+        <v>0.137</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1462</v>
+        <v>-0.156</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3469</v>
+        <v>0.2929</v>
       </c>
       <c r="V16" t="n">
-        <v>5.1419</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>4.3707</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7712</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9349</v>
+        <v>1.3784</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6871</v>
+        <v>2.1918</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7523</v>
+        <v>-0.8134</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2457</v>
+        <v>1.2446</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4806</v>
+        <v>0.4742</v>
       </c>
       <c r="I17" t="n">
-        <v>0.765</v>
+        <v>0.7704</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1892</v>
+        <v>1.1677</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0582</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0565</v>
+        <v>0.077</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4082</v>
+        <v>0.416</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3548</v>
+        <v>-0.2124</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4053</v>
+        <v>-0.0653</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0505</v>
+        <v>-0.1471</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5245</v>
+        <v>-0.269</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5533</v>
+        <v>-3.4418</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0288</v>
+        <v>3.1727</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0054</v>
+        <v>-2.4012</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6478</v>
+        <v>-1.7232</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6424</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2964</v>
+        <v>-2.9607</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7415</v>
+        <v>-1.4931</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4451</v>
+        <v>-1.4676</v>
       </c>
       <c r="M18" t="n">
-        <v>0.291</v>
+        <v>0.5595</v>
       </c>
       <c r="N18" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.2301</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1973</v>
+        <v>0.7896</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0919</v>
+        <v>-0.1685</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6956</v>
+        <v>-0.4811</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6037</v>
+        <v>0.3126</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7071</v>
+        <v>1.3901</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.3901</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9124</v>
+        <v>-0.3711</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7816</v>
+        <v>-2.2282</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8692</v>
+        <v>1.8572</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3973</v>
+        <v>-0.0097</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7229</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6744</v>
+        <v>0.642</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.9469</v>
+        <v>-0.3127</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4861</v>
+        <v>-0.7519</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4608</v>
+        <v>0.4392</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5496</v>
+        <v>0.303</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2368</v>
+        <v>0.1002</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7864</v>
+        <v>0.2028</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8042</v>
+        <v>0.0743</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8347</v>
+        <v>-0.3417</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0305</v>
+        <v>0.416</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3817</v>
+        <v>0.7025</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X19" t="n">
-        <v>1.3817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4913</v>
+        <v>-1.1194</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.5777</v>
+        <v>-4.1322</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0865</v>
+        <v>3.0128</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7667</v>
+        <v>0.7704</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0433</v>
+        <v>-1.0426</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8099</v>
+        <v>1.813</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.223</v>
+        <v>-0.234</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9415</v>
       </c>
       <c r="L20" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9896</v>
+        <v>1.0044</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1009</v>
+        <v>1.1055</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.604</v>
+        <v>-0.2265</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.113</v>
+        <v>-0.6415</v>
       </c>
       <c r="U20" t="n">
-        <v>0.509</v>
+        <v>0.4149</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9645</v>
+        <v>-1.4558</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1064</v>
+        <v>-0.3641</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1419</v>
+        <v>-1.0918</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2963</v>
+        <v>-0.4811</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6552</v>
+        <v>1.2318</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9515</v>
+        <v>-1.7129</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6506</v>
+        <v>2.338</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7171</v>
+        <v>1.5341</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0665</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9469</v>
+        <v>-2.8191</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0619</v>
+        <v>-0.3023</v>
       </c>
       <c r="O21" t="n">
-        <v>0.885</v>
+        <v>-2.5168</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1001</v>
+        <v>-0.6772</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1875</v>
+        <v>-0.5835</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2534</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2832</v>
+        <v>-2.0517</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6884</v>
+        <v>-3.2502</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5947</v>
+        <v>1.1985</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4916</v>
+        <v>0.2931</v>
       </c>
       <c r="H22" t="n">
-        <v>1.225</v>
+        <v>-0.6494</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7166</v>
+        <v>0.9425</v>
       </c>
       <c r="J22" t="n">
-        <v>2.3567</v>
+        <v>-0.6692</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5412</v>
+        <v>-0.7207</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8156</v>
+        <v>0.0515</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8484</v>
+        <v>0.9623</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3162</v>
+        <v>0.0713</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.5321</v>
+        <v>0.8911</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4986</v>
+        <v>-0.1871</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9376</v>
+        <v>-0.3046</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0.1176</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1607</v>
+        <v>-1.2472</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.207</v>
+        <v>-3.8527</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0156</v>
+        <v>0.191</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2226</v>
+        <v>-4.0437</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.369</v>
+        <v>-2.3553</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2873</v>
+        <v>-0.279</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0817</v>
+        <v>-2.0763</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5075</v>
+        <v>-2.4932</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0817</v>
+        <v>-2.0763</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6669</v>
+        <v>-0.0013</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8771</v>
+        <v>0.0531</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2102</v>
+        <v>-0.0545</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3593</v>
+        <v>-4.02</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0473</v>
+        <v>-2.7097</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.312</v>
+        <v>-1.3103</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.1399</v>
+        <v>-5.1268</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7921</v>
+        <v>-1.7922</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.3478</v>
+        <v>-3.3347</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2489</v>
+        <v>-2.2657</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6491</v>
+        <v>-1.6622</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8911</v>
+        <v>-2.8612</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.748</v>
+        <v>-2.7312</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8072</v>
+        <v>-0.4866</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7984</v>
+        <v>-0.4441</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0425</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.846899999999999</v>
+        <v>-4.850799999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.3136</v>
+        <v>-7.624000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4667</v>
+        <v>2.773199999999998</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.5838</v>
+        <v>-8.599600000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.413700000000001</v>
+        <v>-1.4348</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.170299999999999</v>
+        <v>-7.1648</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9231000000000003</v>
+        <v>0.6843000000000008</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1420999999999994</v>
+        <v>-0.2796000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>1.0654</v>
+        <v>0.9638000000000003</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.507299999999999</v>
+        <v>-9.283799999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2718</v>
+        <v>-1.1551</v>
       </c>
       <c r="O25" t="n">
-        <v>-8.235500000000002</v>
+        <v>-8.1287</v>
       </c>
       <c r="P25" t="n">
-        <v>3.4024</v>
+        <v>3.4144</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.4757</v>
+        <v>-12.5197</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.5253</v>
+        <v>-2.5322</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.0525</v>
+        <v>-4.0458</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5273</v>
+        <v>1.5134</v>
       </c>
       <c r="V25" t="n">
-        <v>2.86</v>
+        <v>2.866699999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>8.291600000000001</v>
+        <v>8.2575</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.431699999999999</v>
+        <v>-5.3908</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104490_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104490_W4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.0601</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.4163</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.4846</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.257299999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>1.3901</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104490_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-5.3908</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
